--- a/public/exports-from-60/12881517.xlsx
+++ b/public/exports-from-60/12881517.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253129</t>
+          <t xml:space="preserve">311253147</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">

--- a/public/exports-from-60/12881517.xlsx
+++ b/public/exports-from-60/12881517.xlsx
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257703</t>
+          <t xml:space="preserve">311257933</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">

--- a/public/exports-from-60/12881517.xlsx
+++ b/public/exports-from-60/12881517.xlsx
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253147</t>
+          <t xml:space="preserve">311253129</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257933</t>
+          <t xml:space="preserve">311257703</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
